--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7001bf1f-f6d7-4c24-b746-bd1749d0cebc</t>
+          <t>e43d575c-d90e-4862-8fae-86a3b97679b5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,7 +483,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>d6a69a57-2966-46ba-8639-2b26ba8fea05</t>
+          <t>74727d9e-a930-4500-be57-d63ac0ce9524</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -508,7 +508,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>75cb526b-bcf5-41c9-a34e-1ea320bff89b</t>
+          <t>18aab7f7-96eb-4b02-a0b6-03cb464037b3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>946a4ce5-bd45-425d-a0f4-7ceef8df166a</t>
+          <t>134f173a-a02a-475e-8b91-93d36b94eb32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>d05f55a6-060b-48f2-84b4-411439f46dc7</t>
+          <t>c43553fe-bf65-4055-b481-9fce1e708ea5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
